--- a/MAJSushiConfig/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-administration-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -724,7 +724,7 @@
     <t>MedicationAdministration.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-document|0.1.0)
 </t>
   </si>
   <si>
@@ -961,7 +961,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-condition-document|0.1.0|Observation|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -989,7 +989,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-request-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-request-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1077,7 +1077,7 @@
     <t>sequence</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-administration-sequence-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-sequence-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -1137,7 +1137,7 @@
     <t>EDQM - Standard terms / classe ROA (0.4.0.127.0.16.1.1.2.1)</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-edqm-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-edqm-document|0.1.0</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1589,7 +1589,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="114.53515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="111.3359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
